--- a/data/trans_dic/P79A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P79A_R-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,26</t>
+          <t>0,0; 1,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,39</t>
+          <t>0,0; 5,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 4,34</t>
+          <t>0,13; 2,43</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 9,78</t>
+          <t>2,92; 8,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,92</t>
+          <t>0,91; 2,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,44</t>
+          <t>2,05; 4,9</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,93</t>
+          <t>1,14; 5,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,04</t>
+          <t>1,46; 4,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,01</t>
+          <t>1,68; 4,11</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,03</t>
+          <t>2,74; 10,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,93</t>
+          <t>2,74; 7,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,95</t>
+          <t>3,22; 7,34</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 3,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,36</t>
+          <t>0,09; 1,58</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,7</t>
+          <t>1,18; 5,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,87</t>
+          <t>2,29; 6,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,37</t>
+          <t>2,06; 4,88</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,72</t>
+          <t>0,87; 2,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,34</t>
+          <t>1,67; 4,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,81</t>
+          <t>1,44; 3,04</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,17</t>
+          <t>0,8; 2,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,09</t>
+          <t>0,61; 1,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,79</t>
+          <t>0,89; 2,04</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,77</t>
+          <t>1,88; 3,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,58</t>
+          <t>1,81; 2,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,52</t>
+          <t>1,94; 2,78</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>836</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>4280</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 818</t>
+          <t>0; 4226</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 24300</t>
+          <t>0; 17667</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>170; 26096</t>
+          <t>837; 15435</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>27262</t>
+          <t>26414</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36096</t>
+          <t>35222</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15988; 50685</t>
+          <t>15505; 43116</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4699; 15013</t>
+          <t>4982; 15080</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22930; 56192</t>
+          <t>22038; 52735</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17671</t>
+          <t>18143</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3415; 15581</t>
+          <t>3609; 15784</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5245; 17611</t>
+          <t>5205; 17080</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10612; 26676</t>
+          <t>11301; 27665</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>18796</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>19518</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24672</t>
+          <t>38314</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5006; 18858</t>
+          <t>10213; 38071</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7085; 28208</t>
+          <t>11569; 33467</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15150; 38985</t>
+          <t>25625; 58399</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>539</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>2136</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2848</t>
+          <t>0; 3283</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7516</t>
+          <t>0; 7519</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>361; 5969</t>
+          <t>395; 6884</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>10299</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13778</t>
+          <t>17227</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2158; 12662</t>
+          <t>3203; 13959</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4306; 15083</t>
+          <t>6042; 17835</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8510; 23036</t>
+          <t>10999; 26096</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9734</t>
+          <t>11663</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>17090</t>
+          <t>20701</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26824</t>
+          <t>32364</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4903; 16993</t>
+          <t>6230; 20859</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6193; 28342</t>
+          <t>12875; 32520</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14669; 41344</t>
+          <t>21464; 45317</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>10279</t>
+          <t>11972</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>8876</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19155</t>
+          <t>21956</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3045; 20157</t>
+          <t>6418; 21697</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4851; 14978</t>
+          <t>5043; 16538</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10137; 29528</t>
+          <t>14479; 33212</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>71153</t>
+          <t>85362</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>74199</t>
+          <t>84279</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>145352</t>
+          <t>169641</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>51781; 95956</t>
+          <t>66461; 111769</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>54238; 95737</t>
+          <t>67586; 106853</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>115676; 180662</t>
+          <t>141286; 202044</t>
         </is>
       </c>
     </row>
